--- a/data/catalog_audit.xlsx
+++ b/data/catalog_audit.xlsx
@@ -4913,7 +4913,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, красный</t>
+          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B, красный</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -6021,7 +6021,7 @@
         <v>2000</v>
       </c>
       <c r="E117" t="n">
-        <v>7850</v>
+        <v>7350</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="I117" t="n">
@@ -6323,7 +6323,7 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>7850</v>
+        <v>7350</v>
       </c>
       <c r="E2" t="n">
         <v>7800</v>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Ozon: комплект 7850 ≥ деталей вместе 7800; сайт: комплект 5250 ≤ самой дорогой детали 6220</t>
+          <t>сайт: комплект 5250 ≤ самой дорогой детали 6220</t>
         </is>
       </c>
     </row>
@@ -7576,7 +7576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7625,84 +7625,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>0BH325</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>3850</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>0BH325183</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>7850</v>
-      </c>
-      <c r="D3" t="n">
-        <v>7850</v>
-      </c>
-      <c r="E3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Dq500</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>3850</v>
-      </c>
-      <c r="E4" t="n">
-        <v>69</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Действующий</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7714,7 +7636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7761,7 +7683,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ozon факт 5850 ≠ мастер 5350; WB факт 5850 ≠ Ozon 5350; сайт сейчас 4120, по таблице 2350 (обновится при синхронизации)</t>
+          <t>WB факт 5850 ≠ Ozon 5350; сайт сейчас 4120, по таблице 2350 (обновится при синхронизации)</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7775,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -7873,7 +7795,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, красный</t>
+          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B, красный</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -7941,7 +7863,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ozon факт 3850 ≠ мастер 4850; WB факт 3850 ≠ Ozon 4850; сайт сейчас 2720, по таблице 2250 (обновится при синхронизации)</t>
+          <t>WB факт 3850 ≠ Ozon 4850; сайт сейчас 2720, по таблице 2250 (обновится при синхронизации)</t>
         </is>
       </c>
     </row>
@@ -8042,6 +7964,26 @@
       <c r="D16" t="inlineStr">
         <is>
           <t>сайт сейчас 2720, по таблице 1850 (обновится при синхронизации)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>plita-filtr</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ozon факт 7850 ≠ мастер 7350; WB факт 7850 ≠ Ozon 7350</t>
         </is>
       </c>
     </row>
